--- a/sources/table_normalization/xlsx/education-table35.xlsx
+++ b/sources/table_normalization/xlsx/education-table35.xlsx
@@ -139,17 +139,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -636,24 +637,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>2346756</v>
       </c>
       <c r="B2" s="1"/>
@@ -666,7 +667,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2"/>
+      <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
@@ -677,7 +678,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
@@ -688,7 +689,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
+      <c r="A5" s="3"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
@@ -699,7 +700,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
+      <c r="A6" s="3"/>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
@@ -710,7 +711,7 @@
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
+      <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
@@ -721,7 +722,7 @@
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
+      <c r="A8" s="3"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -732,7 +733,7 @@
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
+      <c r="A9" s="3"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -743,7 +744,7 @@
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2"/>
+      <c r="A10" s="3"/>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
@@ -754,7 +755,7 @@
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>4737888</v>
       </c>
       <c r="B11" s="1"/>
@@ -767,7 +768,7 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2"/>
+      <c r="A12" s="3"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
@@ -778,7 +779,7 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="2"/>
+      <c r="A13" s="3"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
@@ -789,7 +790,7 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="2"/>
+      <c r="A14" s="3"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
@@ -800,7 +801,7 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="2"/>
+      <c r="A15" s="3"/>
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
@@ -811,7 +812,7 @@
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2"/>
+      <c r="A16" s="3"/>
       <c r="B16" s="1" t="s">
         <v>16</v>
       </c>
@@ -822,7 +823,7 @@
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="2"/>
+      <c r="A17" s="3"/>
       <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
@@ -833,7 +834,7 @@
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="2"/>
+      <c r="A18" s="3"/>
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -844,7 +845,7 @@
       <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="2"/>
+      <c r="A19" s="3"/>
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -855,7 +856,7 @@
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="2"/>
+      <c r="A20" s="3"/>
       <c r="B20" s="1" t="s">
         <v>12</v>
       </c>
